--- a/docs/03_Test-Practice/Login/Login_TestCase.xlsx
+++ b/docs/03_Test-Practice/Login/Login_TestCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laypop-sykim\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511B3F4F-D3FF-4FAE-94D2-6687248D0401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD82EC31-8B35-480A-A9E6-753F2C7B6B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="39375" yWindow="8460" windowWidth="26010" windowHeight="11730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="71">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -177,23 +177,6 @@
   </si>
   <si>
     <t>Not Run</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t># 로그인 기능 요구사항
-## 기능
-사용자는 아이디와 비밀번호를 입력하여 로그인할 수 있다.
-## 화면 구성
-- 아이디 입력창
-- 비밀번호 입력창
-- 로그인 버튼
-## 요구사항
-1. 아이디와 비밀번호를 모두 입력한 경우에만 로그인을 시도할 수 있다.
-2. 올바른 아이디와 비밀번호를 입력하면 메인 화면으로 이동한다.
-3. 아이디가 존재하지 않으면 오류 메시지를 표시한다.
-4. 비밀번호가 일치하지 않으면 오류 메시지를 표시한다.
-5. 아이디를 입력하지 않으면 "아이디를 입력하세요."를 표시한다.
-6. 비밀번호를 입력하지 않으면 "비밀번호를 입력하세요."를 표시한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -498,7 +481,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -523,9 +506,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -543,9 +523,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -856,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="24.125" bestFit="1" customWidth="1"/>
@@ -868,562 +845,391 @@
     <col min="11" max="12" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
+      <c r="B2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="12"/>
+      <c r="B3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="12"/>
+      <c r="B4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+      <c r="A5" s="13"/>
+      <c r="B5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="J7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="99" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F29" s="10" t="s">
+      <c r="E16" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G29" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J29" s="11" t="s">
+      <c r="F16" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K29" s="1"/>
-    </row>
-    <row r="30" spans="1:11" ht="99" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K30" s="1"/>
-    </row>
-    <row r="31" spans="1:11" ht="99" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K31" s="1"/>
-    </row>
-    <row r="32" spans="1:11" ht="99" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K32" s="1"/>
-    </row>
-    <row r="33" spans="1:11" ht="99" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K33" s="1"/>
-    </row>
-    <row r="34" spans="1:11" ht="99" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K34" s="1"/>
-    </row>
-    <row r="35" spans="1:11" ht="99" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K35" s="1"/>
-    </row>
-    <row r="36" spans="1:11" ht="99" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K36" s="1"/>
-    </row>
-    <row r="37" spans="1:11" ht="99" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K37" s="1"/>
+      <c r="K16" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="A1:F20"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:A5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="J29:J37">
+  <conditionalFormatting sqref="J8:J16">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
@@ -1438,7 +1244,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J29:J37" xr:uid="{E9BD520C-8C11-4AE7-AF17-95AA569DED0E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J8:J16" xr:uid="{E9BD520C-8C11-4AE7-AF17-95AA569DED0E}">
       <formula1>"P,F,B,N,N/A"</formula1>
     </dataValidation>
   </dataValidations>
